--- a/docs/perechen-otchetov/obrazcy/ФО-56.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-56.xlsx
@@ -7,20 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-56" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-56'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +34,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -52,12 +89,32 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009BC2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -91,50 +148,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,170 +628,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7.8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="8.6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-56</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>на 01.10.2026, с начала 2026 года</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>План-факт освоения кредитов</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.01.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>План выдачи на год</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Выдано с начала года</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитная программа</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Дата последнего освоения</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Освоений</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>План освоения на год</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Освоено за период</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Осталось освоить до плана</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Выполнение плана, %</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Выдач</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Дата выдачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>125000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Региональное представительство «Ош»</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="E8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ОсОО «Достук Строй» · № 26-5/090 от 08.09.2026</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="11" t="n">
+      <c r="F8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="G8" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Департамент администрирования кредитов</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="E9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Отраслевой департамент промышленности</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="G9" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="I9" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>ОсОО «Достук Строй»</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>№ 26-5/090 от 08.09.2026, KGS</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Кредитование строительных проектов</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="33" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-56 · сформировал Бекова Н. С. 06.10.2026 11:40 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -673,7 +961,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>ФО-56 «План-факт освоения кредитов за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>01.01.2026 – 30.09.2026 (по умолчанию — с начала года по вчерашний день)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>справочник «Плановые показатели», показатель «План выдачи» на 2026 год, значение на 30.09.2026: Департамент администрирования кредитов — 5 000 000,00 сом, Департамент регионального развития — 3 000 000,00 сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>Что попадает</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>кредиты с записью освоения в периоде; департаменты с планом на год — и без освоений; департамент, куратор и заёмщик — на 30.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Выполнение плана</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>освоено за период ÷ план на год × 100 по суммам строки; план — в строке департамента и в ИТОГО</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Департамент → Куратор → Заёмщик → кредит → транш</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>освоение в иностранной валюте — по курсу НБКР на день освоения; освоений в иностранной валюте за период нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>В ячейках — точные суммы, на экране и в печати — тыс. сом с двумя знаками, проценты — с одним знаком. Итоги и проценты считаются по точным суммам, поэтому сумма округлённых строк может отличаться от итога на 0,01.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -682,359 +1152,503 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>ФО-56 «План и факт выдачи» — карточка</t>
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>ФО-56 «План-факт освоения кредитов за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>ФО-56</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>План и факт выдачи</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>План-факт освоения кредитов за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Получатель</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Язык</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Основание</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶648–649; ТЗ 05 §8; ТЗ 20 п. 5.32–5.34, 13.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Образец-основа</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="165" customHeight="1">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>Кому и зачем</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Правлению, руководству Холдинга, Департамента администрирования кредитов и Департамента регионального развития — выполнение годового плана выдачи кредитов с начала года: сколько освоено против плана департамента, сколько осталось освоить до плана и по каким кредитам освоение было. План — цель на год, которую утверждает подразделение-владелец справочника «Плановые показатели» и загружает по образцу файла; освоение — записи освоения траншей в карточке кредита. Это единственный отчёт перечня, где видны освоения за период: ФО-08 показывает кредиты, освоение которых на дату не завершено (сколько ещё предстоит выдать по заключённым договорам и какой транш не выдан к плановой дате), ФО-02 «Всего получено» — всё освоенное по кредиту с даты договора, ФО-55 — заявки до договора, ФО-54 — план-факт погашений. Прежнее название — «План и факт выдачи» (общий стартовый отчёт ТЗ 20); в старой системе такого отчёта не было: «Плановые показатели» там — только просмотр плана по заёмщику.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Когда</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>За период, по требованию; по умолчанию — с начала года по вчерашний день. Период — в пределах одного календарного года: план годовой; итог года — период с 01.01 по 31.12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>Параметры</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>• Период — с начала года по вчерашний день; можно выбрать любой отрезок внутри одного календарного года
+• Единица — тыс. сом (можно выбрать «сом»)
+• Разрезы — до шести уровней в любом порядке; по умолчанию департамент → куратор → заёмщик → кредит → транш. Доступны: департамент, отдел, куратор, область, район, отрасль, кредитная программа, кредитная линия, вид кредита, валюта, месяц, заёмщик
+• Отбор — по любому из разрезов; при отборе не по департаменту клетки плана пусты с причиной</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="360" customHeight="1">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>Строки</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Строка детали — транш: кредит с одним траншем на всю сумму договора — одной строкой «№ … от …», при нескольких траншах — строка кредита, под ней «Транш N» по номеру; над кредитом всегда строка заёмщика, даже при одном кредите. В отчёт попадает кредит, у которого в периоде есть запись освоения; транш без освоения в периоде строки не получает. Освоение — только запись освоения транша, рождённого освоением: перенос долга по дополнительному соглашению, производный транш и транш платы за неосвоенный остаток освоением не являются. Не попадают: кредит без освоения в периоде (в том числе зарегистрированный, освоение которого ещё впереди, — он в ФО-08) и расторгнутый до выдачи. Департамент, куратор и заёмщик — на последний день периода, как в ФО-54. План — показатель «План выдачи» справочника «Плановые показатели» на год периода, значение на последний день периода; задан по департаментам (ТЗ 20 п. 5.33): число стоит в строке департамента, когда департамент — первый уровень разрезов, и в ИТОГО (сумма департаментов); на уровнях ниже департамента, у отобранных кредитов и при отборе не по департаменту клетка плана пуста — план на них не делится. Департамент с планом получает строку и без освоений — план, освоено 0,00, выполнение 0,0 % (ТЗ 20 п. 5.34). Выполнение плана — освоено к плану по суммам строки, а не среднее процентов; в ИТОГО — по департаментам с планом, освоение департамента без плана показано справочно. «Осталось освоить до плана» — у строки с планом, в ИТОГО — сумма департаментов. Над кредитами — разрезы, по умолчанию департамент → куратор → заёмщик. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты — по справочнику оргструктуры, в том числе без освоений; кураторы — по алфавиту фамилии; заёмщики — по освоенной сумме от большей, при равных — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора; транши — по номеру. Суммы — в тыс. сом. Кредит в иностранной валюте: каждое освоение — в сомах по курсу на день освоения; под кредитом курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с освоенным в валюте договора, в итоги она не входит; план — в сомах. Печать — A4 альбомная в одну страницу по ширине.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>по умолчанию: Департамент → Куратор → Заёмщик → Кредит → транш; можно выбрать: Департамент, Отдел, Куратор, Область, Район, Отрасль, Кредитная программа, Кредитная линия, Вид кредита, Валюта, Месяц, Заёмщик, Кредит</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Освоений за {период} нет, плана на год в справочнике «Плановые показатели» нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>Выгрузка</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>xlsx, pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>Прежнее название — «План и факт выдачи» (общий стартовый отчёт ТЗ 20 п. 13.15); в старой системе не было. Строка — кредит под департаментом, куратором и заёмщиком: освоено за период против годового плана департамента из справочника «Плановые показатели» (показатель «План выдачи»), осталось освоить до плана, выполнение плана, %; департамент с планом — строкой и без освоений; незавершённое освоение на дату — ФО-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>Колонки</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>Колонка</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Общая шапка</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Что в ней</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr"/>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>департамент, куратор, заёмщик, кредит «№ … от …, KGS», «Транш N» или строка «в тыс. USD (курс …)» — по уровню строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Кредитная программа</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Получатель</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Язык</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Образец-основа</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Кому и зачем</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Руководству и Правлению — выполнение плана выдачи кредитов по подразделениям с начала года.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Когда</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>На дату; по умолчанию сегодня (данные на конец предыдущего дня), период — с 01.01 текущего года; по требованию.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Параметры</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>• Дата — сегодня (данные на конец предыдущего дня; 01.10.2026 = данные на конец 30.09.2026)
-• Подразделение — все
-• Единица — сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Строки</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Подразделение → выдача (освоение). Сверху ИТОГО. Подразделения — по убыванию процента выполнения, при равенстве — по алфавиту; выдачи — по убыванию даты. «Выдано» — освоение кредитов с начала года по дату отчёта. План берётся из справочника «Плановые показатели» и задан по подразделению; в строках выдач план пуст. Процент выполнения считается из сумм уровня: выдано / план × 100.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Выгрузка</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>xlsx, pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Колонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Колонка</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Общая шапка</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Что в ней</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Наименование</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr"/>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>подразделение или выдача: заёмщик, номер договора и транш — по уровню строки</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>План выдачи на год</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>значение справочника «Плановые показатели» на год, сом; задан по подразделению, в строках выдач пусто</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Выдано с начала года</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>сумма освоений с 01.01 по дату отчёта, сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr"/>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>программа, по которой заключён кредит; кредит по индивидуальной заявке — «Без программы»; заполняется у кредита, выше пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Дата последнего освоения</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr"/>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>дата последней записи освоения в периоде: у транша — по нему, у кредита — по всем его траншам; выше кредита пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>Заёмщиков</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr"/>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>число заёмщиков с освоением в периоде; у заёмщика и ниже пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Кредитов</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr"/>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>число кредитов с освоением в периоде; у кредита и ниже пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Освоений</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr"/>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>число записей освоения с датой в периоде: у транша — его записи, выше — сумма строк ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>План освоения на год</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr"/>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>показатель «План выдачи» справочника «Плановые показатели» на год периода, значение на последний день периода; план задан по департаментам — число стоит в строке департамента и в ИТОГО (сумма департаментов), на уровнях ниже департамента и при отборе не по департаменту — пусто: на них план не делится; у департамента без плана — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Освоено за период</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr"/>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>сумма записей освоения с датой в периоде — только транши, рождённые освоением; перенос по дополнительному соглашению, производный транш и транш платы за неосвоенный остаток освоением не являются; у кредита в иностранной валюте — каждое освоение в сомах по курсу на день освоения</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>Осталось освоить до плана</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr"/>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>«План освоения на год» − «Освоено за период», если больше нуля, иначе 0,00; только в строке с планом; в ИТОГО — сумма по департаментам: перевыполнение одного департамента остаток другого не закрывает</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Выполнение плана, %</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr"/>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>выдано / план × 100, один знак; в строках выдач пусто</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Выдач</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>число освоений (выдач) за период</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Дата выдачи</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr"/>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>дата освоения; на уровне подразделения и в ИТОГО пусто</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr"/>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>«Освоено за период» ÷ «План освоения на год» × 100 по суммам строки, один знак; в ИТОГО — освоено департаментами с планом ÷ сумма их планов: освоение департамента без плана в процент не входит, оно показано справочно; где плана нет — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>„План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>01.01–30.09.2026: заёмщиков 1, кредитов 1, освоений 1; план освоения на 2026 год 8 000,000 тыс. сом; освоено 1 500,000; осталось освоить до плана 6 500,000; выполнение плана 18,8 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>„Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>План — справочник «Плановые показатели», показатель «План выдачи» на 2026 год (общая заметка набора): Департамент администрирования кредитов 5 000,000, Департамент регионального развития 3 000,000; ИТОГО плана 8 000,000 = сумма департаментов. В строках куратора, заёмщика и кредита план пуст.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>КЗ-17 ОсОО «Достук Строй» № 26-5/090 от 08.09.2026 (Департамент регионального развития, Осмонов Б. Т., программа «Кредитование строительных проектов»): одно освоение 15.09.2026 — 1 500,000, транш один на всю сумму договора, поэтому одна строка кредита; освоено = «Всего получено» ФО-02 (1 500,000), кредит освоен полностью и в ФО-08 не попадает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития: 1 500,000 ÷ 3 000,000 = 50,0 %, осталось 1 500,000. Департамент администрирования кредитов: освоений в периоде нет, строка — из справочника плана (ТЗ 20 п. 5.34): план 5 000,000, освоено 0,00, осталось 5 000,000, выполнение 0,0 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>Выполнение — по суммам строки, не среднее: ИТОГО 1 500,000 ÷ 8 000,000 = 18,8 %, а не (0,0 + 50,0) ÷ 2 = 25,0 %; «Осталось освоить» ИТОГО 6 500,000 = 5 000,000 + 1 500,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>Не попадают: КЗ-26 № 26-3/118 от 20.08.2026 (ДАК) — освоений нет, транш 1 (1 200,000) к плановой дате 01.09.2026 не выдан — он в ФО-08; КЗ-18 № 26-1/012 — расторгнут 10.09.2026 до выдачи; КЗ-12 — освоения 20.03.2024 и 25.06.2024 вне периода; дополнительное соглашение КЗ-06 от 08.09.2026 освоением не является; остальные кредиты набора освоены до 2026 года.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>Разрез «Месяц» первым уровнем: сентябрь 2026 — 1 освоение, 1 500,000; в строках месяцев план пуст — план годовой и по месяцам не делится; в ИТОГО — 8 000,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Отбор «Кредитная программа: Кредитование строительных проектов»: КЗ-17, освоено 1 500,000; клетки плана, остатка и выполнения пусты с причиной «план задан по департаментам: на отобранные кредиты он не делится»; строка «Отбор: …» под заголовком.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по кредитам, освоениям и освоенной сумме; заёмщики — число заёмщиков разреза; проценты — из сумм строки.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="25">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
